--- a/output/laminas_comunales/comunal_o_ocup_a_2024_la_araucania.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2024_la_araucania.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C225"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,46 +375,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Temuco</t>
+          <t>Angol</t>
         </is>
       </c>
       <c r="C2">
-        <v>36.4195814154703</v>
+        <v>56.7828715750804</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Renaico</t>
+          <t>Temuco</t>
         </is>
       </c>
       <c r="C3">
-        <v>35.0329829877221</v>
+        <v>56.5000557615636</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Angol</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="C4">
-        <v>34.9014759794266</v>
+        <v>55.6714200831848</v>
       </c>
     </row>
     <row r="5">
@@ -429,427 +429,3307 @@
         </is>
       </c>
       <c r="C5">
-        <v>32.6252044199893</v>
+        <v>52.1624365482233</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Padre Las Casas</t>
+          <t>Collipulli</t>
         </is>
       </c>
       <c r="C6">
-        <v>32.2360280094918</v>
+        <v>50.9396103177239</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9202</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Collipulli</t>
+          <t>Pitrufquén</t>
         </is>
       </c>
       <c r="C7">
-        <v>31.7306317895941</v>
+        <v>50.6392202341506</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vilcún</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="C8">
-        <v>30.4985441374902</v>
+        <v>50.5146807053587</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Perquenco</t>
         </is>
       </c>
       <c r="C9">
-        <v>30.4927749047649</v>
+        <v>50.307855626327</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Perquenco</t>
+          <t>Padre Las Casas</t>
         </is>
       </c>
       <c r="C10">
-        <v>29.8946997178557</v>
+        <v>49.7094876418411</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9114</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pitrufquén</t>
+          <t>Temuco</t>
         </is>
       </c>
       <c r="C11">
-        <v>29.4108620229517</v>
+        <v>48.9354662583605</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pucón</t>
+          <t>Los Sauces</t>
         </is>
       </c>
       <c r="C12">
-        <v>28.9366370655571</v>
+        <v>48.5481043173351</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9105</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Freire</t>
+          <t>Traiguén</t>
         </is>
       </c>
       <c r="C13">
-        <v>28.5461139896373</v>
+        <v>48.3572725771834</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Villarrica</t>
+          <t>Vilcún</t>
         </is>
       </c>
       <c r="C14">
-        <v>28.5420140267302</v>
+        <v>48.3244059881884</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Loncoche</t>
+          <t>Freire</t>
         </is>
       </c>
       <c r="C15">
-        <v>27.8707199583388</v>
+        <v>48.1407643688345</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Los Sauces</t>
+          <t>Loncoche</t>
         </is>
       </c>
       <c r="C16">
-        <v>27.8613912593742</v>
+        <v>47.6631712167782</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ercilla</t>
+          <t>Angol</t>
         </is>
       </c>
       <c r="C17">
-        <v>27.7207776996955</v>
+        <v>47.2078308768796</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Galvarino</t>
+          <t>Gorbea</t>
         </is>
       </c>
       <c r="C18">
-        <v>27.5225732122284</v>
+        <v>46.5689635470232</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Traiguén</t>
+          <t>Purén</t>
         </is>
       </c>
       <c r="C19">
-        <v>27.4883224727524</v>
+        <v>46.2201971572673</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Purén</t>
+          <t>Villarrica</t>
         </is>
       </c>
       <c r="C20">
-        <v>26.2078539126453</v>
+        <v>46.1084524962495</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Gorbea</t>
+          <t>Nueva Imperial</t>
         </is>
       </c>
       <c r="C21">
-        <v>25.9426464456952</v>
+        <v>45.8725610588075</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nueva Imperial</t>
+          <t>Galvarino</t>
         </is>
       </c>
       <c r="C22">
-        <v>25.9018545872312</v>
+        <v>45.1220170607926</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9204</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lumaco</t>
+          <t>Ercilla</t>
         </is>
       </c>
       <c r="C23">
-        <v>25.7584246347942</v>
+        <v>45.0170357751278</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9121</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cholchol</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="C24">
-        <v>24.4524925436728</v>
+        <v>44.5888660307961</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Curacautín</t>
+          <t>Renaico</t>
         </is>
       </c>
       <c r="C25">
-        <v>24.0297782350251</v>
+        <v>44.2157654022061</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cunco</t>
+          <t>Lumaco</t>
         </is>
       </c>
       <c r="C26">
-        <v>23.8762967650386</v>
+        <v>43.9891439757964</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>9118</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Toltén</t>
+          <t>Curacautín</t>
         </is>
       </c>
       <c r="C27">
-        <v>23.4555219146482</v>
+        <v>43.780105973025</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9205</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lonquimay</t>
+          <t>Cunco</t>
         </is>
       </c>
       <c r="C28">
-        <v>23.2109557109557</v>
+        <v>42.8707801787729</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Melipeuco</t>
+          <t>Toltén</t>
         </is>
       </c>
       <c r="C29">
-        <v>22.9965034965035</v>
+        <v>42.8046811945117</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Carahue</t>
+          <t>Melipeuco</t>
         </is>
       </c>
       <c r="C30">
-        <v>22.4843881482794</v>
+        <v>42.3387096774194</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>9115</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Curarrehue</t>
+          <t>Pucón</t>
         </is>
       </c>
       <c r="C31">
-        <v>21.8899625663794</v>
+        <v>42.3063870223308</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Teodoro Schmidt</t>
+          <t>Carahue</t>
         </is>
       </c>
       <c r="C32">
-        <v>20.3860482755544</v>
+        <v>41.7441648431802</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>41.5044773391813</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>41.0190142145099</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>40.8863034430571</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>40.5076536713705</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>9101</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>40.4837108435114</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>40.1502596398188</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>39.5432692307692</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>9201</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>39.2148713358057</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>39.1713773738269</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>38.811773255814</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>38.7341320781629</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>38.4911275831087</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>38.4225883968417</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>38.0560633759902</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>37.5996321275291</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>37.5767813267813</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>36.7710350763934</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>36.723259762309</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>36.7086058891704</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>9116</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Saavedra</t>
         </is>
       </c>
-      <c r="C33">
+      <c r="C52">
+        <v>36.5458243598947</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>36.5195161491458</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>9101</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>36.4195814154703</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>35.997521685254</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>35.7449183409705</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>35.6512255920233</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>35.3650479022134</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>35.3191856452726</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>9209</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Renaico</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>35.0329829877221</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>34.9256051521208</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>9201</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>34.9014759794266</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>34.3539445063399</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>34.3261371712864</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>33.6333540244155</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>33.505376344086</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>33.4263000702741</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>33.224027938184</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>32.9959680737267</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>32.856210749531</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>9101</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>32.8214169016011</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>32.6252044199893</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>32.2360280094918</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>31.8901060685098</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>31.8810025767159</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>31.8173973075595</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>31.804210849854</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>31.7687665343915</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>31.7306317895941</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>31.6688778997306</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>31.1785319070454</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>9201</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>30.8983133546966</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>30.4985441374902</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>30.4927749047649</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>30.1533090467517</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>30.1511954992968</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>9209</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Renaico</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>30.0642554319025</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>29.9094097019287</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>29.8946997178557</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>29.784103410341</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>29.6358032456913</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>29.4108620229517</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>29.4054742907801</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>28.9366370655571</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>28.8556271314892</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>28.721881390593</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>28.5461139896373</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>28.5420140267302</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>28.3456108041743</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>28.2550486468809</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>27.9899135446686</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>27.9349816849817</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>27.8707199583388</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>27.868337505635</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>27.8613912593742</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>27.7207776996955</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>9101</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>27.5580977645141</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>27.5225732122284</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>27.5163626505557</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>27.4883224727524</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>27.4782654792197</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>27.3529642255398</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>9201</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>27.1900948991696</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>27.1148459383753</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>27.0006217938753</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>26.9671528373575</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>26.5223235156615</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>26.4889399468397</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>26.3586043468265</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>26.2900242377854</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>26.2328395953757</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>26.2078539126453</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>26.0436432637571</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>25.9426464456952</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>25.9018545872312</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>25.8296055901529</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>25.8159641209105</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>25.8058008164815</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>25.7584246347942</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>25.7407407407407</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>25.7225088372982</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>25.7090113049729</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>25.6927520534344</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>25.6000468329235</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>25.2904564315353</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>25.2628560504684</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>9209</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Renaico</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>25.2333461194221</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>25.0747084548105</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>24.6970348087667</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>24.6269966649114</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>24.5912186012616</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>24.5463857184665</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>24.5246831220814</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>24.4524925436728</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>24.4083378845804</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>24.2842917600199</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>24.2522490945204</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>24.0297782350251</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>23.8762967650386</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>23.7729770703051</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>23.658379373849</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>23.4555219146482</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>23.2750582750583</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>23.2109557109557</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>22.9965034965035</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>22.8994231251568</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>22.8274912931131</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>22.7718132242672</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>22.7208172988822</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>22.4856834143706</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>22.4846504258269</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>22.4843881482794</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>22.4461789175744</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>22.3962773515203</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>22.2323153675347</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>22.1463227783453</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>22.0912193608439</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>21.8899625663794</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>21.8606278744251</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>21.7377006051039</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>21.6547773454388</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>21.6216818100837</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>21.4840090994246</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>21.3301662707838</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>21.2046204620462</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>21.0934696806602</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>21.0563638027267</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>21.0355987055016</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>20.8847851077243</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>20.8831085420681</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>20.7843466577091</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>20.7287368179734</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>20.673291292439</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>20.6151965777144</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>20.4168112923753</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>20.3860482755544</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>20.3063278638712</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>19.7486275642878</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C189">
         <v>19.6207397283676</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>19.0724339476352</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>19.0334623893805</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>18.526848865501</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>18.4051542036333</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>9209</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Renaico</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>10.4402286270218</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>9.716346675344401</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>9101</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>9.62436576682645</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>9201</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>9.494224046207631</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Ercilla</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>9.42792792792793</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Perquenco</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>9.299582652876071</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>9112</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Padre Las Casas</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>8.73344030280589</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>9211</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>8.63004776378637</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Vilcún</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>8.476245376375079</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>9108</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>8.31495976187851</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>9206</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Los Sauces</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>8.01000172443525</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>9105</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Freire</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>7.89355144618303</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>9115</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>7.86662168241116</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>7.85484262972415</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>9114</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>7.53853564547206</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>9106</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>7.43488794669897</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>9109</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>7.41840478949401</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>9120</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>7.19607964382884</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>9207</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Lumaco</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>7.12752254186346</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Purén</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>6.37946562593816</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>9107</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>6.10244097639056</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>9111</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>6.09677906011918</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>6.06350864971555</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>9103</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>6.01860027076343</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>9203</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Curacautín</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>6.00923131546245</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>9205</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>5.96011722731906</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>9121</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Cholchol</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>5.27505446623094</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Melipeuco</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>5.22427242724272</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>9102</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>5.0257536736858</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>9104</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Curarrehue</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>4.80469391104546</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Teodoro Schmidt</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>4.46854741041533</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>3.50793216630197</v>
       </c>
     </row>
   </sheetData>
